--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,6 +1092,782 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126022047</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91679</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Telemarkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>557988</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7012119</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126022051</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Telemarkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>557963</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7012006</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126022054</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98332</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Telemarkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>557935</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7012019</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126022052</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Telemarkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>557944</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7012013</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126022053</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Telemarkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>557944</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7012013</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126022055</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98355</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Telemarkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557935</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7012019</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126022049</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91521</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>658</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Telemarkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>557948</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7012056</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126022050</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79586</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Telemarkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557972</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7012006</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>126022047</v>
       </c>
       <c r="B6" t="n">
-        <v>91679</v>
+        <v>91682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022055</v>
+        <v>126022049</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>91524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557935</v>
+        <v>557948</v>
       </c>
       <c r="R11" t="n">
-        <v>7012019</v>
+        <v>7012056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022049</v>
+        <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>91521</v>
+        <v>98357</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557948</v>
+        <v>557935</v>
       </c>
       <c r="R12" t="n">
-        <v>7012056</v>
+        <v>7012019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>126022047</v>
       </c>
       <c r="B6" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126022051</v>
       </c>
       <c r="B7" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>126022052</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126022053</v>
       </c>
       <c r="B10" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>126022049</v>
       </c>
       <c r="B11" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>126022050</v>
       </c>
       <c r="B13" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022049</v>
+        <v>126022055</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>98362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557948</v>
+        <v>557935</v>
       </c>
       <c r="R11" t="n">
-        <v>7012056</v>
+        <v>7012019</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022055</v>
+        <v>126022049</v>
       </c>
       <c r="B12" t="n">
-        <v>98362</v>
+        <v>91528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557935</v>
+        <v>557948</v>
       </c>
       <c r="R12" t="n">
-        <v>7012019</v>
+        <v>7012056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022055</v>
+        <v>126022049</v>
       </c>
       <c r="B11" t="n">
-        <v>98362</v>
+        <v>91528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557935</v>
+        <v>557948</v>
       </c>
       <c r="R11" t="n">
-        <v>7012019</v>
+        <v>7012056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022049</v>
+        <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>91528</v>
+        <v>98362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557948</v>
+        <v>557935</v>
       </c>
       <c r="R12" t="n">
-        <v>7012056</v>
+        <v>7012019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>126022047</v>
       </c>
       <c r="B6" t="n">
-        <v>91686</v>
+        <v>91688</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126022051</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>126022052</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126022053</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>126022049</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>126022050</v>
       </c>
       <c r="B13" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>126022047</v>
       </c>
       <c r="B6" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>126022049</v>
       </c>
       <c r="B11" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>126022047</v>
       </c>
       <c r="B6" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>126022049</v>
       </c>
       <c r="B11" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>126022047</v>
       </c>
       <c r="B6" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126022051</v>
       </c>
       <c r="B7" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>126022052</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126022053</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>126022049</v>
       </c>
       <c r="B11" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>126022050</v>
       </c>
       <c r="B13" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>126022047</v>
       </c>
       <c r="B6" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126022051</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>126022054</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>126022052</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126022053</v>
       </c>
       <c r="B10" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022049</v>
+        <v>126022055</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>98384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557948</v>
+        <v>557935</v>
       </c>
       <c r="R11" t="n">
-        <v>7012056</v>
+        <v>7012019</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022055</v>
+        <v>126022049</v>
       </c>
       <c r="B12" t="n">
-        <v>98375</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557935</v>
+        <v>557948</v>
       </c>
       <c r="R12" t="n">
-        <v>7012019</v>
+        <v>7012056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
         <v>126022050</v>
       </c>
       <c r="B13" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022055</v>
+        <v>126022049</v>
       </c>
       <c r="B11" t="n">
-        <v>98384</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557935</v>
+        <v>557948</v>
       </c>
       <c r="R11" t="n">
-        <v>7012019</v>
+        <v>7012056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022049</v>
+        <v>126022055</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>98384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557948</v>
+        <v>557935</v>
       </c>
       <c r="R12" t="n">
-        <v>7012056</v>
+        <v>7012019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022049</v>
+        <v>126022055</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>98384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557948</v>
+        <v>557935</v>
       </c>
       <c r="R11" t="n">
-        <v>7012056</v>
+        <v>7012019</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022055</v>
+        <v>126022049</v>
       </c>
       <c r="B12" t="n">
-        <v>98384</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557935</v>
+        <v>557948</v>
       </c>
       <c r="R12" t="n">
-        <v>7012019</v>
+        <v>7012056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113027275</v>
+        <v>126022049</v>
       </c>
       <c r="B2" t="n">
-        <v>89604</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5754</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vattenberget, Jmt</t>
+          <t>Telemarkberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557937</v>
+        <v>557948</v>
       </c>
       <c r="R2" t="n">
-        <v>7011981</v>
+        <v>7012056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,66 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113027228</v>
+        <v>126022047</v>
       </c>
       <c r="B3" t="n">
-        <v>97314</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vattenberget, Jmt</t>
+          <t>Telemarkberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557974</v>
+        <v>557988</v>
       </c>
       <c r="R3" t="n">
-        <v>7012014</v>
+        <v>7012119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,31 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113027280</v>
+        <v>113027279</v>
       </c>
       <c r="B4" t="n">
-        <v>91320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,19 +880,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6047725</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -989,37 +970,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113027279</v>
+        <v>113027275</v>
       </c>
       <c r="B5" t="n">
-        <v>90972</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>5754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557938</v>
+        <v>557937</v>
       </c>
       <c r="R5" t="n">
-        <v>7011975</v>
+        <v>7011981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126022047</v>
+        <v>126022052</v>
       </c>
       <c r="B6" t="n">
-        <v>91699</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557988</v>
+        <v>557944</v>
       </c>
       <c r="R6" t="n">
-        <v>7012119</v>
+        <v>7012013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022051</v>
+        <v>126022053</v>
       </c>
       <c r="B7" t="n">
-        <v>78739</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557963</v>
+        <v>557944</v>
       </c>
       <c r="R7" t="n">
-        <v>7012006</v>
+        <v>7012013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,32 +1265,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022054</v>
+        <v>126022050</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557935</v>
+        <v>557972</v>
       </c>
       <c r="R8" t="n">
-        <v>7012019</v>
+        <v>7012006</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,32 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126022052</v>
+        <v>126022055</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>99142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557944</v>
+        <v>557935</v>
       </c>
       <c r="R9" t="n">
-        <v>7012013</v>
+        <v>7012019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,45 +1459,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126022053</v>
+        <v>113027228</v>
       </c>
       <c r="B10" t="n">
-        <v>78738</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Telemarkberget, Jmt</t>
+          <t>Vattenberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557944</v>
+        <v>557973</v>
       </c>
       <c r="R10" t="n">
-        <v>7012013</v>
+        <v>7012014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,12 +1524,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,44 +1544,48 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022055</v>
+        <v>126022054</v>
       </c>
       <c r="B11" t="n">
-        <v>98384</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1657,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022049</v>
+        <v>126022051</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>79085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1668,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557948</v>
+        <v>557963</v>
       </c>
       <c r="R12" t="n">
-        <v>7012056</v>
+        <v>7012006</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,10 +1754,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126022050</v>
+        <v>113027280</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>93211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,34 +1765,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6047725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Telemarkberget, Jmt</t>
+          <t>Vattenberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557972</v>
+        <v>557938</v>
       </c>
       <c r="R13" t="n">
-        <v>7012006</v>
+        <v>7011975</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,12 +1815,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,15 +1835,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9347-2024 artfynd.xlsx
+++ b/artfynd/A 9347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022049</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022047</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113027279</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113027275</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022052</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022053</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022050</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022055</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113027228</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022054</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022051</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,8 +1908,27 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113027280</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>